--- a/backend/templates/base/base_proctor.xlsx
+++ b/backend/templates/base/base_proctor.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="165" formatCode="0.000&quot; g/cm³&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,7 +77,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -99,6 +99,12 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -183,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -237,6 +243,9 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -249,14 +258,14 @@
     <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -886,7 +895,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>GOBIERNO REGIONAL CUSCO</t>
@@ -900,28 +909,28 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="12" customHeight="1">
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>SUB GERENCIA DE COBERTURA Y COMUNICACIONES</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="12" customHeight="1">
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>UNIDAD FUNCIONAL ESTUDIOS Y PROYECTOS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Laboratorio de Mecánica de Suelos, Materiales y Pavimentos</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="12" customHeight="1">
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>«Año de la recuperación y consolidación de la economía peruana»</t>
@@ -945,7 +954,7 @@
       <c r="I8" s="7" t="n"/>
     </row>
     <row r="9" ht="6" customHeight="1"/>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>PROYECTO</t>
@@ -960,7 +969,7 @@
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>UBICACIÓN</t>
@@ -991,7 +1000,7 @@
       </c>
       <c r="I11" s="10" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>SOLICITANTE</t>
@@ -1008,7 +1017,7 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
@@ -1033,7 +1042,7 @@
       </c>
       <c r="I13" s="10" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>DATOS DE MUESTRA</t>
@@ -1156,130 +1165,130 @@
       <c r="I20" s="17" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Masa del molde (g)</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Masa molde + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Agua incrementada (g)</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Masa del suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="22">
         <f>IF(COUNT(B22:B23)=2,B23-B22,"")</f>
         <v/>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="22">
         <f>IF(COUNT(C22:C23)=2,C23-C22,"")</f>
         <v/>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="22">
         <f>IF(COUNT(D22:D23)=2,D23-D22,"")</f>
         <v/>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="22">
         <f>IF(COUNT(E22:E23)=2,E23-E22,"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Volumen del molde (cm³)</t>
         </is>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="22">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="22">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="22">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="22">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Densidad húmeda (g/cm³)</t>
         </is>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="23">
         <f>IF(AND(ISNUMBER(B25),N(B26)&gt;0),IFERROR(B25/B26,0),"")</f>
         <v/>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="23">
         <f>IF(AND(ISNUMBER(C25),N(C26)&gt;0),IFERROR(C25/C26,0),"")</f>
         <v/>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="23">
         <f>IF(AND(ISNUMBER(D25),N(D26)&gt;0),IFERROR(D25/D26,0),"")</f>
         <v/>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="23">
         <f>IF(AND(ISNUMBER(E25),N(E26)&gt;0),IFERROR(E25/E26,0),"")</f>
         <v/>
       </c>
@@ -1301,164 +1310,164 @@
       <c r="I30" s="17" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Cápsula N°</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Masa de cápsula (g)</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="20" t="n"/>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Masa cápsula + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n"/>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Masa cápsula + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="20" t="n"/>
+      <c r="B35" s="21" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Masa de agua (g)</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <f>IF(COUNT(B34:B35)=2,B34-B35,"")</f>
         <v/>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="22">
         <f>IF(COUNT(C34:C35)=2,C34-C35,"")</f>
         <v/>
       </c>
-      <c r="D36" s="21">
+      <c r="D36" s="22">
         <f>IF(COUNT(D34:D35)=2,D34-D35,"")</f>
         <v/>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="22">
         <f>IF(COUNT(E34:E35)=2,E34-E35,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Masa de suelo seco (g)</t>
         </is>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="22">
         <f>IF(COUNT(B33,B35)=2,B35-B33,"")</f>
         <v/>
       </c>
-      <c r="C37" s="21">
+      <c r="C37" s="22">
         <f>IF(COUNT(C33,C35)=2,C35-C33,"")</f>
         <v/>
       </c>
-      <c r="D37" s="21">
+      <c r="D37" s="22">
         <f>IF(COUNT(D33,D35)=2,D35-D33,"")</f>
         <v/>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="22">
         <f>IF(COUNT(E33,E35)=2,E35-E33,"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Contenido de humedad (%)</t>
         </is>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="22">
         <f>IF(AND(ISNUMBER(B37),N(B37)&gt;0),IFERROR(B36/B37*100,0),"")</f>
         <v/>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="22">
         <f>IF(AND(ISNUMBER(C37),N(C37)&gt;0),IFERROR(C36/C37*100,0),"")</f>
         <v/>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="22">
         <f>IF(AND(ISNUMBER(D37),N(D37)&gt;0),IFERROR(D36/D37*100,0),"")</f>
         <v/>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="22">
         <f>IF(AND(ISNUMBER(E37),N(E37)&gt;0),IFERROR(E36/E37*100,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Densidad seca (g/cm³)</t>
         </is>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="23">
         <f>IF(AND(ISNUMBER(B38),ISNUMBER(B27)),IFERROR(B27/(1+B38/100),0),"")</f>
         <v/>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="23">
         <f>IF(AND(ISNUMBER(C38),ISNUMBER(C27)),IFERROR(C27/(1+C38/100),0),"")</f>
         <v/>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="23">
         <f>IF(AND(ISNUMBER(D38),ISNUMBER(D27)),IFERROR(D27/(1+D38/100),0),"")</f>
         <v/>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="23">
         <f>IF(AND(ISNUMBER(E38),ISNUMBER(E27)),IFERROR(E27/(1+E38/100),0),"")</f>
         <v/>
       </c>
@@ -1469,7 +1478,7 @@
           <t>MÁXIMA DENSIDAD SECA (g/cm³)</t>
         </is>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="24">
         <f>IF(ISNUMBER(_DATOS!$F$5),_DATOS!$F$5,"")</f>
         <v/>
       </c>
@@ -1483,7 +1492,7 @@
           <t>HUMEDAD ÓPTIMA (%)</t>
         </is>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="25">
         <f>IF(ISNUMBER(_DATOS!$F$4),_DATOS!$F$4,"")</f>
         <v/>
       </c>
@@ -1508,28 +1517,28 @@
       <c r="I45" s="17" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="25" t="n"/>
-      <c r="B76" s="25" t="n"/>
-      <c r="C76" s="25" t="n"/>
-      <c r="D76" s="25" t="n"/>
-      <c r="E76" s="25" t="n"/>
-      <c r="F76" s="25" t="n"/>
-      <c r="G76" s="25" t="n"/>
-      <c r="H76" s="25" t="n"/>
-      <c r="I76" s="25" t="n"/>
+      <c r="A76" s="26" t="n"/>
+      <c r="B76" s="26" t="n"/>
+      <c r="C76" s="26" t="n"/>
+      <c r="D76" s="26" t="n"/>
+      <c r="E76" s="26" t="n"/>
+      <c r="F76" s="26" t="n"/>
+      <c r="G76" s="26" t="n"/>
+      <c r="H76" s="26" t="n"/>
+      <c r="I76" s="26" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="26" t="inlineStr">
+      <c r="A77" s="27" t="inlineStr">
         <is>
           <t>ESP. ENSAYOS GEOTECNICOS</t>
         </is>
       </c>
-      <c r="D77" s="26" t="inlineStr">
+      <c r="D77" s="27" t="inlineStr">
         <is>
           <t>ESP. SUELOS Y PAVIMENTOS</t>
         </is>
       </c>
-      <c r="G77" s="26" t="inlineStr">
+      <c r="G77" s="27" t="inlineStr">
         <is>
           <t>SUPERVISOR</t>
         </is>
@@ -1539,15 +1548,16 @@
   <mergeCells count="23">
     <mergeCell ref="A8"/>
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
     <mergeCell ref="B41:E41"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C1:G1"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C2:G2"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C1:F1"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="A77:C77"/>
@@ -1557,7 +1567,6 @@
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="C2:F2"/>
     <mergeCell ref="D77:F77"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>

--- a/backend/templates/base/base_proctor.xlsx
+++ b/backend/templates/base/base_proctor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Reporte" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_DATOS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="_GRAFICOS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="_MAPA" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DATOS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_GRAFICOS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_MAPA" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="CurvaX">'_DATOS'!$A$3:$A$6</definedName>
@@ -345,13 +345,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -372,7 +372,7 @@
             <v>Ajuste Cuadrático</v>
           </tx>
           <spPr>
-            <a:ln w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
               <a:solidFill>
                 <a:srgbClr val="DC2626"/>
               </a:solidFill>
@@ -382,7 +382,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -406,7 +406,7 @@
             <v>Puntos de Ensayo</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -415,10 +415,10 @@
             <symbol val="circle"/>
             <size val="8"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E40AF"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="1E40AF"/>
                 </a:solidFill>
@@ -445,7 +445,7 @@
             <v>Máxima Densidad Seca</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -454,10 +454,10 @@
             <symbol val="circle"/>
             <size val="10"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="059669"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="059669"/>
                 </a:solidFill>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -531,9 +531,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -553,13 +553,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -578,13 +578,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/backend/templates/base/base_proctor.xlsx
+++ b/backend/templates/base/base_proctor.xlsx
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -218,7 +218,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,6 +234,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1053,41 +1056,41 @@
           <t>Explor.:</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n"/>
+      <c r="C14" s="16" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Progresiva:</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n"/>
+      <c r="E14" s="16" t="n"/>
       <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Estrato:</t>
         </is>
       </c>
-      <c r="G14" s="10" t="n"/>
+      <c r="G14" s="16" t="n"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Lado:</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n"/>
+      <c r="I14" s="16" t="n"/>
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>COMPACTACIÓN PROCTOR MODIFICADO - MTC E 115</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="17" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1100,25 +1103,25 @@
           <t>Código:</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n"/>
+      <c r="C17" s="16" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Diám. (cm):</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n"/>
+      <c r="E17" s="16" t="n"/>
       <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Altura (cm):</t>
         </is>
       </c>
-      <c r="G17" s="10" t="n"/>
+      <c r="G17" s="16" t="n"/>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Vol. (cm³):</t>
         </is>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="19">
         <f>IF(AND(N(E17)&gt;0,N(G17)&gt;0),ROUND(PI()*POWER(E17,2)*G17/4,1),"")</f>
         <v/>
       </c>
@@ -1134,340 +1137,340 @@
           <t>Golpes/capa:</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n"/>
+      <c r="C18" s="16" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>N° capas:</t>
         </is>
       </c>
-      <c r="E18" s="10" t="n"/>
+      <c r="E18" s="16" t="n"/>
       <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Martillo (lb):</t>
         </is>
       </c>
-      <c r="G18" s="10" t="n"/>
+      <c r="G18" s="16" t="n"/>
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>DATOS DE ENSAYO</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="17" t="n"/>
-      <c r="H20" s="17" t="n"/>
-      <c r="I20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Masa del molde (g)</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Masa molde + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n"/>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Agua incrementada (g)</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Masa del suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="23">
         <f>IF(COUNT(B22:B23)=2,B23-B22,"")</f>
         <v/>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>IF(COUNT(C22:C23)=2,C23-C22,"")</f>
         <v/>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <f>IF(COUNT(D22:D23)=2,D23-D22,"")</f>
         <v/>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="23">
         <f>IF(COUNT(E22:E23)=2,E23-E22,"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Volumen del molde (cm³)</t>
         </is>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="23">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="23">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="23">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Densidad húmeda (g/cm³)</t>
         </is>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="24">
         <f>IF(AND(ISNUMBER(B25),N(B26)&gt;0),IFERROR(B25/B26,0),"")</f>
         <v/>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="24">
         <f>IF(AND(ISNUMBER(C25),N(C26)&gt;0),IFERROR(C25/C26,0),"")</f>
         <v/>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="24">
         <f>IF(AND(ISNUMBER(D25),N(D26)&gt;0),IFERROR(D25/D26,0),"")</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <f>IF(AND(ISNUMBER(E25),N(E26)&gt;0),IFERROR(E25/E26,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="6" customHeight="1"/>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>CÁLCULO DE LA HUMEDAD</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="17" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Cápsula N°</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n"/>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Masa de cápsula (g)</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Masa cápsula + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Masa cápsula + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Masa de agua (g)</t>
         </is>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="23">
         <f>IF(COUNT(B34:B35)=2,B34-B35,"")</f>
         <v/>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="23">
         <f>IF(COUNT(C34:C35)=2,C34-C35,"")</f>
         <v/>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="23">
         <f>IF(COUNT(D34:D35)=2,D34-D35,"")</f>
         <v/>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="23">
         <f>IF(COUNT(E34:E35)=2,E34-E35,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Masa de suelo seco (g)</t>
         </is>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="23">
         <f>IF(COUNT(B33,B35)=2,B35-B33,"")</f>
         <v/>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="23">
         <f>IF(COUNT(C33,C35)=2,C35-C33,"")</f>
         <v/>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="23">
         <f>IF(COUNT(D33,D35)=2,D35-D33,"")</f>
         <v/>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="23">
         <f>IF(COUNT(E33,E35)=2,E35-E33,"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Contenido de humedad (%)</t>
         </is>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="23">
         <f>IF(AND(ISNUMBER(B37),N(B37)&gt;0),IFERROR(B36/B37*100,0),"")</f>
         <v/>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="23">
         <f>IF(AND(ISNUMBER(C37),N(C37)&gt;0),IFERROR(C36/C37*100,0),"")</f>
         <v/>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="23">
         <f>IF(AND(ISNUMBER(D37),N(D37)&gt;0),IFERROR(D36/D37*100,0),"")</f>
         <v/>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="23">
         <f>IF(AND(ISNUMBER(E37),N(E37)&gt;0),IFERROR(E36/E37*100,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Densidad seca (g/cm³)</t>
         </is>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="24">
         <f>IF(AND(ISNUMBER(B38),ISNUMBER(B27)),IFERROR(B27/(1+B38/100),0),"")</f>
         <v/>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="24">
         <f>IF(AND(ISNUMBER(C38),ISNUMBER(C27)),IFERROR(C27/(1+C38/100),0),"")</f>
         <v/>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="24">
         <f>IF(AND(ISNUMBER(D38),ISNUMBER(D27)),IFERROR(D27/(1+D38/100),0),"")</f>
         <v/>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="24">
         <f>IF(AND(ISNUMBER(E38),ISNUMBER(E27)),IFERROR(E27/(1+E38/100),0),"")</f>
         <v/>
       </c>
@@ -1478,7 +1481,7 @@
           <t>MÁXIMA DENSIDAD SECA (g/cm³)</t>
         </is>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="25">
         <f>IF(ISNUMBER(_DATOS!$F$5),_DATOS!$F$5,"")</f>
         <v/>
       </c>
@@ -1492,7 +1495,7 @@
           <t>HUMEDAD ÓPTIMA (%)</t>
         </is>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="26">
         <f>IF(ISNUMBER(_DATOS!$F$4),_DATOS!$F$4,"")</f>
         <v/>
       </c>
@@ -1502,43 +1505,43 @@
     </row>
     <row r="43" ht="6" customHeight="1"/>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>CURVA DE COMPACTACIÓN</t>
         </is>
       </c>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="17" t="n"/>
-      <c r="G45" s="17" t="n"/>
-      <c r="H45" s="17" t="n"/>
-      <c r="I45" s="17" t="n"/>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="n"/>
-      <c r="B76" s="26" t="n"/>
-      <c r="C76" s="26" t="n"/>
-      <c r="D76" s="26" t="n"/>
-      <c r="E76" s="26" t="n"/>
-      <c r="F76" s="26" t="n"/>
-      <c r="G76" s="26" t="n"/>
-      <c r="H76" s="26" t="n"/>
-      <c r="I76" s="26" t="n"/>
+      <c r="A76" s="27" t="n"/>
+      <c r="B76" s="27" t="n"/>
+      <c r="C76" s="27" t="n"/>
+      <c r="D76" s="27" t="n"/>
+      <c r="E76" s="27" t="n"/>
+      <c r="F76" s="27" t="n"/>
+      <c r="G76" s="27" t="n"/>
+      <c r="H76" s="27" t="n"/>
+      <c r="I76" s="27" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="27" t="inlineStr">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>ESP. ENSAYOS GEOTECNICOS</t>
         </is>
       </c>
-      <c r="D77" s="27" t="inlineStr">
+      <c r="D77" s="28" t="inlineStr">
         <is>
           <t>ESP. SUELOS Y PAVIMENTOS</t>
         </is>
       </c>
-      <c r="G77" s="27" t="inlineStr">
+      <c r="G77" s="28" t="inlineStr">
         <is>
           <t>SUPERVISOR</t>
         </is>

--- a/backend/templates/base/base_proctor.xlsx
+++ b/backend/templates/base/base_proctor.xlsx
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -256,6 +256,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1178,21 +1181,25 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
+      <c r="I21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -1201,9 +1208,13 @@
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
+      <c r="C22" s="21" t="n"/>
       <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
@@ -1212,9 +1223,13 @@
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
+      <c r="C23" s="21" t="n"/>
       <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
@@ -1223,9 +1238,13 @@
         </is>
       </c>
       <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
+      <c r="C24" s="21" t="n"/>
       <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
@@ -1237,18 +1256,22 @@
         <f>IF(COUNT(B22:B23)=2,B23-B22,"")</f>
         <v/>
       </c>
-      <c r="C25" s="23">
-        <f>IF(COUNT(C22:C23)=2,C23-C22,"")</f>
-        <v/>
-      </c>
+      <c r="C25" s="24" t="n"/>
       <c r="D25" s="23">
         <f>IF(COUNT(D22:D23)=2,D23-D22,"")</f>
         <v/>
       </c>
-      <c r="E25" s="23">
-        <f>IF(COUNT(E22:E23)=2,E23-E22,"")</f>
-        <v/>
-      </c>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="23">
+        <f>IF(COUNT(F22:F23)=2,F23-F22,"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="23">
+        <f>IF(COUNT(H22:H23)=2,H23-H22,"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="24" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
@@ -1260,18 +1283,22 @@
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="C26" s="23">
-        <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
-        <v/>
-      </c>
+      <c r="C26" s="24" t="n"/>
       <c r="D26" s="23">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="23">
         <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
         <v/>
       </c>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="23">
+        <f>IF(N($I$17)&gt;0,$I$17,2124)</f>
+        <v/>
+      </c>
+      <c r="I26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -1279,22 +1306,26 @@
           <t>Densidad húmeda (g/cm³)</t>
         </is>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="25">
         <f>IF(AND(ISNUMBER(B25),N(B26)&gt;0),IFERROR(B25/B26,0),"")</f>
         <v/>
       </c>
-      <c r="C27" s="24">
-        <f>IF(AND(ISNUMBER(C25),N(C26)&gt;0),IFERROR(C25/C26,0),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="25">
         <f>IF(AND(ISNUMBER(D25),N(D26)&gt;0),IFERROR(D25/D26,0),"")</f>
         <v/>
       </c>
-      <c r="E27" s="24">
-        <f>IF(AND(ISNUMBER(E25),N(E26)&gt;0),IFERROR(E25/E26,0),"")</f>
-        <v/>
-      </c>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="25">
+        <f>IF(AND(ISNUMBER(F25),N(F26)&gt;0),IFERROR(F25/F26,0),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="25">
+        <f>IF(AND(ISNUMBER(H25),N(H26)&gt;0),IFERROR(H25/H26,0),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="24" t="n"/>
     </row>
     <row r="28" ht="6" customHeight="1"/>
     <row r="30">
@@ -1323,21 +1354,25 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
+      <c r="I31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
@@ -1349,6 +1384,10 @@
       <c r="C32" s="21" t="n"/>
       <c r="D32" s="21" t="n"/>
       <c r="E32" s="21" t="n"/>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="21" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
@@ -1357,9 +1396,13 @@
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
+      <c r="C33" s="21" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -1368,9 +1411,13 @@
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
+      <c r="C34" s="21" t="n"/>
       <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="21" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
@@ -1379,9 +1426,13 @@
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
+      <c r="C35" s="21" t="n"/>
       <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -1393,18 +1444,22 @@
         <f>IF(COUNT(B34:B35)=2,B34-B35,"")</f>
         <v/>
       </c>
-      <c r="C36" s="23">
-        <f>IF(COUNT(C34:C35)=2,C34-C35,"")</f>
-        <v/>
-      </c>
+      <c r="C36" s="24" t="n"/>
       <c r="D36" s="23">
         <f>IF(COUNT(D34:D35)=2,D34-D35,"")</f>
         <v/>
       </c>
-      <c r="E36" s="23">
-        <f>IF(COUNT(E34:E35)=2,E34-E35,"")</f>
-        <v/>
-      </c>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="23">
+        <f>IF(COUNT(F34:F35)=2,F34-F35,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="23">
+        <f>IF(COUNT(H34:H35)=2,H34-H35,"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="24" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
@@ -1416,18 +1471,22 @@
         <f>IF(COUNT(B33,B35)=2,B35-B33,"")</f>
         <v/>
       </c>
-      <c r="C37" s="23">
-        <f>IF(COUNT(C33,C35)=2,C35-C33,"")</f>
-        <v/>
-      </c>
+      <c r="C37" s="24" t="n"/>
       <c r="D37" s="23">
         <f>IF(COUNT(D33,D35)=2,D35-D33,"")</f>
         <v/>
       </c>
-      <c r="E37" s="23">
-        <f>IF(COUNT(E33,E35)=2,E35-E33,"")</f>
-        <v/>
-      </c>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="23">
+        <f>IF(COUNT(F33,F35)=2,F35-F33,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="24" t="n"/>
+      <c r="H37" s="23">
+        <f>IF(COUNT(H33,H35)=2,H35-H33,"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
@@ -1439,18 +1498,22 @@
         <f>IF(AND(ISNUMBER(B37),N(B37)&gt;0),IFERROR(B36/B37*100,0),"")</f>
         <v/>
       </c>
-      <c r="C38" s="23">
-        <f>IF(AND(ISNUMBER(C37),N(C37)&gt;0),IFERROR(C36/C37*100,0),"")</f>
-        <v/>
-      </c>
+      <c r="C38" s="24" t="n"/>
       <c r="D38" s="23">
         <f>IF(AND(ISNUMBER(D37),N(D37)&gt;0),IFERROR(D36/D37*100,0),"")</f>
         <v/>
       </c>
-      <c r="E38" s="23">
-        <f>IF(AND(ISNUMBER(E37),N(E37)&gt;0),IFERROR(E36/E37*100,0),"")</f>
-        <v/>
-      </c>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="23">
+        <f>IF(AND(ISNUMBER(F37),N(F37)&gt;0),IFERROR(F36/F37*100,0),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="23">
+        <f>IF(AND(ISNUMBER(H37),N(H37)&gt;0),IFERROR(H36/H37*100,0),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="24" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
@@ -1458,22 +1521,26 @@
           <t>Densidad seca (g/cm³)</t>
         </is>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="25">
         <f>IF(AND(ISNUMBER(B38),ISNUMBER(B27)),IFERROR(B27/(1+B38/100),0),"")</f>
         <v/>
       </c>
-      <c r="C39" s="24">
-        <f>IF(AND(ISNUMBER(C38),ISNUMBER(C27)),IFERROR(C27/(1+C38/100),0),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="24">
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="25">
         <f>IF(AND(ISNUMBER(D38),ISNUMBER(D27)),IFERROR(D27/(1+D38/100),0),"")</f>
         <v/>
       </c>
-      <c r="E39" s="24">
-        <f>IF(AND(ISNUMBER(E38),ISNUMBER(E27)),IFERROR(E27/(1+E38/100),0),"")</f>
-        <v/>
-      </c>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="25">
+        <f>IF(AND(ISNUMBER(F38),ISNUMBER(F27)),IFERROR(F27/(1+F38/100),0),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="25">
+        <f>IF(AND(ISNUMBER(H38),ISNUMBER(H27)),IFERROR(H27/(1+H38/100),0),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="24" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1481,13 +1548,17 @@
           <t>MÁXIMA DENSIDAD SECA (g/cm³)</t>
         </is>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="26">
         <f>IF(ISNUMBER(_DATOS!$F$5),_DATOS!$F$5,"")</f>
         <v/>
       </c>
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="9" t="n"/>
       <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -1495,13 +1566,17 @@
           <t>HUMEDAD ÓPTIMA (%)</t>
         </is>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="27">
         <f>IF(ISNUMBER(_DATOS!$F$4),_DATOS!$F$4,"")</f>
         <v/>
       </c>
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+      <c r="I42" s="9" t="n"/>
     </row>
     <row r="43" ht="6" customHeight="1"/>
     <row r="45">
@@ -1520,58 +1595,122 @@
       <c r="I45" s="18" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="27" t="n"/>
-      <c r="B76" s="27" t="n"/>
-      <c r="C76" s="27" t="n"/>
-      <c r="D76" s="27" t="n"/>
-      <c r="E76" s="27" t="n"/>
-      <c r="F76" s="27" t="n"/>
-      <c r="G76" s="27" t="n"/>
-      <c r="H76" s="27" t="n"/>
-      <c r="I76" s="27" t="n"/>
+      <c r="A76" s="28" t="n"/>
+      <c r="B76" s="28" t="n"/>
+      <c r="C76" s="28" t="n"/>
+      <c r="D76" s="28" t="n"/>
+      <c r="E76" s="28" t="n"/>
+      <c r="F76" s="28" t="n"/>
+      <c r="G76" s="28" t="n"/>
+      <c r="H76" s="28" t="n"/>
+      <c r="I76" s="28" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="28" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>ESP. ENSAYOS GEOTECNICOS</t>
         </is>
       </c>
-      <c r="D77" s="28" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>ESP. SUELOS Y PAVIMENTOS</t>
         </is>
       </c>
-      <c r="G77" s="28" t="inlineStr">
+      <c r="G77" s="29" t="inlineStr">
         <is>
           <t>SUPERVISOR</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A8"/>
+  <mergeCells count="87">
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
     <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="G12:I12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="D77:F77"/>
     <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A8"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1635,11 +1774,11 @@
     </row>
     <row r="4">
       <c r="A4">
-        <f>IF(OR(NOT(ISNUMBER(Reporte!C38)),NOT(ISNUMBER(Reporte!C39)),Reporte!C39=0),NA(),Reporte!C38)</f>
+        <f>IF(OR(NOT(ISNUMBER(Reporte!D38)),NOT(ISNUMBER(Reporte!D39)),Reporte!D39=0),NA(),Reporte!D38)</f>
         <v/>
       </c>
       <c r="B4">
-        <f>IF(ISNA(A4),NA(),Reporte!C39)</f>
+        <f>IF(ISNA(A4),NA(),Reporte!D39)</f>
         <v/>
       </c>
       <c r="F4">
@@ -1657,11 +1796,11 @@
     </row>
     <row r="5">
       <c r="A5">
-        <f>IF(OR(NOT(ISNUMBER(Reporte!D38)),NOT(ISNUMBER(Reporte!D39)),Reporte!D39=0),NA(),Reporte!D38)</f>
+        <f>IF(OR(NOT(ISNUMBER(Reporte!F38)),NOT(ISNUMBER(Reporte!F39)),Reporte!F39=0),NA(),Reporte!F38)</f>
         <v/>
       </c>
       <c r="B5">
-        <f>IF(ISNA(A5),NA(),Reporte!D39)</f>
+        <f>IF(ISNA(A5),NA(),Reporte!F39)</f>
         <v/>
       </c>
       <c r="F5">
@@ -1679,11 +1818,11 @@
     </row>
     <row r="6">
       <c r="A6">
-        <f>IF(OR(NOT(ISNUMBER(Reporte!E38)),NOT(ISNUMBER(Reporte!E39)),Reporte!E39=0),NA(),Reporte!E38)</f>
+        <f>IF(OR(NOT(ISNUMBER(Reporte!H38)),NOT(ISNUMBER(Reporte!H39)),Reporte!H39=0),NA(),Reporte!H38)</f>
         <v/>
       </c>
       <c r="B6">
-        <f>IF(ISNA(A6),NA(),Reporte!E39)</f>
+        <f>IF(ISNA(A6),NA(),Reporte!H39)</f>
         <v/>
       </c>
       <c r="H6">
@@ -2644,7 +2783,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2666,7 +2805,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2688,7 +2827,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2710,7 +2849,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>F22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2732,7 +2871,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2754,7 +2893,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2776,7 +2915,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>H22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2798,7 +2937,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>H23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2820,7 +2959,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>H24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2925,7 +3064,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2942,7 +3081,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2964,7 +3103,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2986,7 +3125,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3008,7 +3147,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3025,7 +3164,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>F33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3047,7 +3186,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>F34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3069,7 +3208,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>F35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3091,7 +3230,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>H32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3108,7 +3247,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>E33</t>
+          <t>H33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3130,7 +3269,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>E34</t>
+          <t>H34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3152,7 +3291,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>E35</t>
+          <t>H35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">

--- a/backend/templates/base/base_proctor.xlsx
+++ b/backend/templates/base/base_proctor.xlsx
@@ -158,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,6 +179,50 @@
       <bottom style="thin">
         <color rgb="000F172A"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <top style="thin">
@@ -218,15 +262,14 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -236,14 +279,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,7 +310,7 @@
     <xf numFmtId="166" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1014,14 +1054,14 @@
       </c>
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Fecha Muestreo:</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -1035,12 +1075,14 @@
         </is>
       </c>
       <c r="C13" s="10" t="n"/>
+      <c r="D13" s="13" t="n"/>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>N:</t>
         </is>
       </c>
       <c r="F13" s="10" t="n"/>
+      <c r="G13" s="13" t="n"/>
       <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Prof. (m):</t>
@@ -1059,25 +1101,25 @@
           <t>Explor.:</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n"/>
+      <c r="C14" s="11" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Progresiva:</t>
         </is>
       </c>
-      <c r="E14" s="16" t="n"/>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Estrato:</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n"/>
+      <c r="G14" s="11" t="n"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Lado:</t>
         </is>
       </c>
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="11" t="n"/>
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
@@ -1106,19 +1148,19 @@
           <t>Código:</t>
         </is>
       </c>
-      <c r="C17" s="16" t="n"/>
+      <c r="C17" s="11" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Diám. (cm):</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n"/>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Altura (cm):</t>
         </is>
       </c>
-      <c r="G17" s="16" t="n"/>
+      <c r="G17" s="11" t="n"/>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Vol. (cm³):</t>
@@ -1140,19 +1182,21 @@
           <t>Golpes/capa:</t>
         </is>
       </c>
-      <c r="C18" s="16" t="n"/>
+      <c r="C18" s="11" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>N° capas:</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n"/>
+      <c r="E18" s="11" t="n"/>
       <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Martillo (lb):</t>
         </is>
       </c>
-      <c r="G18" s="16" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="13" t="n"/>
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20">
@@ -1623,7 +1667,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="88">
     <mergeCell ref="H35:I35"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C5:G5"/>
@@ -1688,6 +1732,7 @@
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="C6:G6"/>
+    <mergeCell ref="G18:I18"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="F24:G24"/>
